--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20211.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -73,58 +73,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ARIZMENDI</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
+    <t>DE JESUS</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>VALENCIA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>NUÑEZ</t>
-  </si>
-  <si>
-    <t>DE LOS SANTOS</t>
+    <t>SORIANO</t>
   </si>
   <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>KARLA IRAN</t>
-  </si>
-  <si>
-    <t>MARTIN</t>
+    <t>JESUS</t>
   </si>
   <si>
     <t>MONSERRAT</t>
-  </si>
-  <si>
-    <t>MAURICIO</t>
-  </si>
-  <si>
-    <t>LUIS ARIEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
   </si>
 </sst>
 </file>
@@ -525,19 +489,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>65.79000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -551,19 +515,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>59.38</v>
+        <v>84.38</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -577,19 +541,19 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>77.27</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
     </row>
   </sheetData>
@@ -642,16 +606,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>38</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>84.20999999999999</v>
+      </c>
+      <c r="H2">
+        <v>8.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -665,16 +632,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>84.38</v>
+      </c>
+      <c r="H3">
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -688,16 +658,19 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>63.64</v>
+      </c>
+      <c r="H4">
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -750,19 +723,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>65.79000000000001</v>
+        <v>86.84</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -776,19 +749,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>59.38</v>
+        <v>84.38</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -802,19 +775,19 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>77.27</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -824,7 +797,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -856,39 +829,39 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920042</v>
+        <v>19330051920010</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920056</v>
+        <v>19330051920081</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -897,99 +870,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920081</v>
-      </c>
-      <c r="B4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>19330051920037</v>
-      </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-      <c r="G5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>19330051920049</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>28</v>
-      </c>
-      <c r="D6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>19330051920068</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20211.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20211.xlsx
@@ -870,7 +870,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20211.xlsx
+++ b/docentes/Vargas Olvera Francisco Eduardo - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -73,22 +73,79 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>SORIANO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>JESUS</t>
-  </si>
-  <si>
-    <t>MONSERRAT</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>CITLAHUA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>SERRANO</t>
+  </si>
+  <si>
+    <t>VALDERRAMA</t>
+  </si>
+  <si>
+    <t>CONDADO</t>
+  </si>
+  <si>
+    <t>BERISTAIN</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>MONTERO</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>ALAN EDUARDO</t>
+  </si>
+  <si>
+    <t>ALEXIS YAIR</t>
+  </si>
+  <si>
+    <t>RAUL ARTURO</t>
+  </si>
+  <si>
+    <t>JUAN ANTONIO</t>
+  </si>
+  <si>
+    <t>EDUARDO</t>
+  </si>
+  <si>
+    <t>YAMIL ELIEL</t>
+  </si>
+  <si>
+    <t>EMILIO</t>
+  </si>
+  <si>
+    <t>JOSUE ALEXIS</t>
   </si>
 </sst>
 </file>
@@ -489,19 +546,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G2">
-        <v>86.84</v>
+        <v>89.47</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -515,10 +572,10 @@
         <v>32</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>5</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>27</v>
@@ -527,7 +584,7 @@
         <v>84.38</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -541,19 +598,19 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>77.27</v>
+        <v>86.36</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -606,19 +663,19 @@
         <v>38</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G2">
-        <v>84.20999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="H2">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -632,10 +689,10 @@
         <v>32</v>
       </c>
       <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
         <v>5</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3">
         <v>27</v>
@@ -644,7 +701,7 @@
         <v>84.38</v>
       </c>
       <c r="H3">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -658,19 +715,19 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>3</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>63.64</v>
+        <v>86.36</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>6.9</v>
       </c>
     </row>
   </sheetData>
@@ -723,10 +780,10 @@
         <v>38</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>5</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>33</v>
@@ -735,7 +792,7 @@
         <v>86.84</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -749,19 +806,19 @@
         <v>32</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -775,19 +832,19 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>77.27</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -797,7 +854,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -829,16 +886,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920010</v>
+        <v>19330051920014</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -847,30 +904,191 @@
         <v>9</v>
       </c>
       <c r="G2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920081</v>
+        <v>19330051920039</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920067</v>
+      </c>
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>19330051920091</v>
+      </c>
+      <c r="B5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>19330051920098</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>19330051920109</v>
+      </c>
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
-        <v>5</v>
+      <c r="C7" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>19330051920032</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>19330051920036</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>19330051920093</v>
+      </c>
+      <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
